--- a/tests-dotnet/fixtures/etp-sample/R008_Banking_Details.xlsx
+++ b/tests-dotnet/fixtures/etp-sample/R008_Banking_Details.xlsx
@@ -541,7 +541,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>20260827</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
